--- a/data/indicadores/10_04_02_04_gin.xlsx
+++ b/data/indicadores/10_04_02_04_gin.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\ods_paolo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{281CDA1A-C4F2-4950-B8F6-34783939AB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE2566E8-BA72-4D0E-9DEA-DD80CE52E3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Procesados" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="Indicador_DEP" sheetId="3" r:id="rId4"/>
     <sheet name="Absoluto_DEP" sheetId="6" r:id="rId5"/>
     <sheet name="Umbral" sheetId="4" r:id="rId6"/>
-    <sheet name="Mapa" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1566,7 +1565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1612,6 +1611,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1627,72 +1627,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>236219</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>361720</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA10D557-2294-03E6-D47B-286B560CAC06}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="236219" y="152400"/>
-          <a:ext cx="6465341" cy="4366260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1948,7 +1882,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="22">
-        <v>0.32364869048414957</v>
+        <v>0.32415030590832128</v>
       </c>
       <c r="F2" s="22">
         <v>0.28256671869200756</v>
@@ -2006,7 +1940,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="22">
-        <v>0.53317705928957704</v>
+        <v>0.53211451230235118</v>
       </c>
       <c r="F4" s="22">
         <v>0.47523350811944609</v>
@@ -2667,7 +2601,7 @@
         <v>46</v>
       </c>
       <c r="E33" s="22">
-        <v>0.37694821279832147</v>
+        <v>0.37686619454156611</v>
       </c>
       <c r="F33" s="22">
         <v>0.30974064333034046</v>
@@ -2687,7 +2621,7 @@
         <v>47</v>
       </c>
       <c r="E34" s="22">
-        <v>0.36393707492427674</v>
+        <v>0.36406996179141071</v>
       </c>
       <c r="F34" s="22">
         <v>0.28758415588875175</v>
@@ -2767,7 +2701,7 @@
         <v>52</v>
       </c>
       <c r="E38" s="22">
-        <v>0.39795199871819609</v>
+        <v>0.41899975770908138</v>
       </c>
       <c r="F38" s="22">
         <v>0.2785161521668813</v>
@@ -2787,7 +2721,7 @@
         <v>53</v>
       </c>
       <c r="E39" s="22">
-        <v>0.41899975770908138</v>
+        <v>0.3856209690805521</v>
       </c>
       <c r="F39" s="22">
         <v>0.31306334003963232</v>
@@ -2807,7 +2741,7 @@
         <v>54</v>
       </c>
       <c r="E40" s="22">
-        <v>0.3856209690805521</v>
+        <v>0.29134830816997548</v>
       </c>
       <c r="F40" s="22">
         <v>0.29562332521555268</v>
@@ -2827,7 +2761,7 @@
         <v>55</v>
       </c>
       <c r="E41" s="22">
-        <v>0.29134830816997548</v>
+        <v>0.39795199871819609</v>
       </c>
       <c r="F41" s="22">
         <v>0.24351124918692268</v>
@@ -3827,7 +3761,7 @@
         <v>114</v>
       </c>
       <c r="E91" s="22">
-        <v>0.42465930262092888</v>
+        <v>0.42824323701692113</v>
       </c>
       <c r="F91" s="22">
         <v>0.31411012204024358</v>
@@ -3887,7 +3821,7 @@
         <v>117</v>
       </c>
       <c r="E94" s="22">
-        <v>0.45381854383355225</v>
+        <v>0.44569873680022631</v>
       </c>
       <c r="F94" s="22">
         <v>0.30227875151761907</v>
@@ -5087,7 +5021,7 @@
         <v>192</v>
       </c>
       <c r="E154" s="22">
-        <v>0.52497402750570421</v>
+        <v>0.49936823811783082</v>
       </c>
       <c r="F154" s="22">
         <v>0.43634086273994832</v>
@@ -5146,8 +5080,8 @@
       <c r="D157" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="E157" s="22">
-        <v>0.52497402750570421</v>
+      <c r="E157" s="27">
+        <v>0.5806565037883944</v>
       </c>
       <c r="F157" s="22">
         <v>0.52008469807361846</v>
@@ -5407,7 +5341,7 @@
         <v>209</v>
       </c>
       <c r="E170" s="22">
-        <v>0.45942809937489182</v>
+        <v>0.45935901141992153</v>
       </c>
       <c r="F170" s="22">
         <v>0.38097447645090732</v>
@@ -5927,7 +5861,7 @@
         <v>244</v>
       </c>
       <c r="E196" s="22">
-        <v>0.39458137172763941</v>
+        <v>0.39021216311876938</v>
       </c>
       <c r="F196" s="22">
         <v>0.34052269183378825</v>
@@ -6247,7 +6181,7 @@
         <v>264</v>
       </c>
       <c r="E212" s="22">
-        <v>0.59355260125654552</v>
+        <v>0.58300014429381131</v>
       </c>
       <c r="F212" s="22">
         <v>0.53938052176219164</v>
@@ -6267,7 +6201,7 @@
         <v>265</v>
       </c>
       <c r="E213" s="22">
-        <v>0.62960634198439247</v>
+        <v>0.62892469757546143</v>
       </c>
       <c r="F213" s="22">
         <v>0.56360552443267364</v>
@@ -6327,7 +6261,7 @@
         <v>268</v>
       </c>
       <c r="E216" s="22">
-        <v>0.59355260125654552</v>
+        <v>0.59086275011740108</v>
       </c>
       <c r="F216" s="22">
         <v>0.50039866371748865</v>
@@ -6687,7 +6621,7 @@
         <v>294</v>
       </c>
       <c r="E234" s="22">
-        <v>0.41675936884162867</v>
+        <v>0.38985334037328956</v>
       </c>
       <c r="F234" s="22">
         <v>0.33330607111754285</v>
@@ -6724,8 +6658,8 @@
       <c r="D236" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="E236" s="22">
-        <v>0.41675936884162867</v>
+      <c r="E236" s="27">
+        <v>0.45482646164121632</v>
       </c>
       <c r="F236" s="22">
         <v>0.36826737508883856</v>
@@ -7085,7 +7019,7 @@
         <v>324</v>
       </c>
       <c r="E254" s="22">
-        <v>0.25798079085832115</v>
+        <v>0.25760621194354938</v>
       </c>
       <c r="F254" s="22">
         <v>0.24767890683233218</v>
@@ -7105,7 +7039,7 @@
         <v>325</v>
       </c>
       <c r="E255" s="22">
-        <v>0.34430386524300105</v>
+        <v>0.33532090457607477</v>
       </c>
       <c r="F255" s="22">
         <v>0.2838412847523748</v>
@@ -7945,7 +7879,7 @@
         <v>375</v>
       </c>
       <c r="E297" s="22">
-        <v>0.36742739086084253</v>
+        <v>0.4275552259460691</v>
       </c>
       <c r="F297" s="22">
         <v>0.32384501252762754</v>
@@ -7965,7 +7899,7 @@
         <v>376</v>
       </c>
       <c r="E298" s="22">
-        <v>0.4275552259460691</v>
+        <v>0.36278560288231398</v>
       </c>
       <c r="F298" s="22">
         <v>0.37954899367730932</v>
@@ -7985,7 +7919,7 @@
         <v>377</v>
       </c>
       <c r="E299" s="22">
-        <v>0.36278560288231398</v>
+        <v>0.36742739086084253</v>
       </c>
       <c r="F299" s="22">
         <v>0.31071946390496508</v>
@@ -8365,7 +8299,7 @@
         <v>402</v>
       </c>
       <c r="E318" s="22">
-        <v>0.35148003017679819</v>
+        <v>0.34476973526209553</v>
       </c>
       <c r="F318" s="22">
         <v>0.31441849730859461</v>
@@ -8405,7 +8339,7 @@
         <v>405</v>
       </c>
       <c r="E320" s="22">
-        <v>0.38729062960357785</v>
+        <v>0.37880350555847242</v>
       </c>
       <c r="F320" s="22">
         <v>0.34476693812893178</v>
@@ -8582,9 +8516,8 @@
       <c r="D329" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="E329" s="22">
-        <f>AVERAGE(E318,E320)</f>
-        <v>0.36938532989018802</v>
+      <c r="E329" s="27">
+        <v>0.44178384833265194</v>
       </c>
       <c r="F329" s="22">
         <v>0.42700849385463879</v>
@@ -10588,7 +10521,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="22">
-        <v>0.32364869048414957</v>
+        <v>0.32415030590832128</v>
       </c>
       <c r="D2" s="22">
         <v>0.28256671869200756</v>
@@ -10624,7 +10557,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="22">
-        <v>0.53317705928957704</v>
+        <v>0.53211451230235118</v>
       </c>
       <c r="D4" s="22">
         <v>0.47523350811944609</v>
@@ -11030,7 +10963,7 @@
         <v>46</v>
       </c>
       <c r="C33" s="22">
-        <v>0.37694821279832147</v>
+        <v>0.37686619454156611</v>
       </c>
       <c r="D33" s="22">
         <v>0.30974064333034046</v>
@@ -11044,7 +10977,7 @@
         <v>47</v>
       </c>
       <c r="C34" s="22">
-        <v>0.36393707492427674</v>
+        <v>0.36406996179141071</v>
       </c>
       <c r="D34" s="22">
         <v>0.28758415588875175</v>
@@ -11100,7 +11033,7 @@
         <v>52</v>
       </c>
       <c r="C38" s="22">
-        <v>0.39795199871819609</v>
+        <v>0.41899975770908138</v>
       </c>
       <c r="D38" s="22">
         <v>0.2785161521668813</v>
@@ -11114,7 +11047,7 @@
         <v>53</v>
       </c>
       <c r="C39" s="22">
-        <v>0.41899975770908138</v>
+        <v>0.3856209690805521</v>
       </c>
       <c r="D39" s="22">
         <v>0.31306334003963232</v>
@@ -11128,7 +11061,7 @@
         <v>54</v>
       </c>
       <c r="C40" s="22">
-        <v>0.3856209690805521</v>
+        <v>0.29134830816997548</v>
       </c>
       <c r="D40" s="22">
         <v>0.29562332521555268</v>
@@ -11142,7 +11075,7 @@
         <v>55</v>
       </c>
       <c r="C41" s="22">
-        <v>0.29134830816997548</v>
+        <v>0.39795199871819609</v>
       </c>
       <c r="D41" s="22">
         <v>0.24351124918692268</v>
@@ -11842,7 +11775,7 @@
         <v>114</v>
       </c>
       <c r="C91" s="22">
-        <v>0.42465930262092888</v>
+        <v>0.42824323701692113</v>
       </c>
       <c r="D91" s="22">
         <v>0.31411012204024358</v>
@@ -11884,7 +11817,7 @@
         <v>117</v>
       </c>
       <c r="C94" s="22">
-        <v>0.45381854383355225</v>
+        <v>0.44569873680022631</v>
       </c>
       <c r="D94" s="22">
         <v>0.30227875151761907</v>
@@ -12724,7 +12657,7 @@
         <v>192</v>
       </c>
       <c r="C154" s="22">
-        <v>0.52497402750570421</v>
+        <v>0.49936823811783082</v>
       </c>
       <c r="D154" s="22">
         <v>0.43634086273994832</v>
@@ -12766,7 +12699,7 @@
         <v>195</v>
       </c>
       <c r="C157" s="22">
-        <v>0.52497402750570421</v>
+        <v>0.5806565037883944</v>
       </c>
       <c r="D157" s="22">
         <v>0.52008469807361846</v>
@@ -12948,7 +12881,7 @@
         <v>209</v>
       </c>
       <c r="C170" s="22">
-        <v>0.45942809937489182</v>
+        <v>0.45935901141992153</v>
       </c>
       <c r="D170" s="22">
         <v>0.38097447645090732</v>
@@ -13312,7 +13245,7 @@
         <v>244</v>
       </c>
       <c r="C196" s="22">
-        <v>0.39458137172763941</v>
+        <v>0.39021216311876938</v>
       </c>
       <c r="D196" s="22">
         <v>0.34052269183378825</v>
@@ -13536,7 +13469,7 @@
         <v>264</v>
       </c>
       <c r="C212" s="22">
-        <v>0.59355260125654552</v>
+        <v>0.58300014429381131</v>
       </c>
       <c r="D212" s="22">
         <v>0.53938052176219164</v>
@@ -13550,7 +13483,7 @@
         <v>265</v>
       </c>
       <c r="C213" s="22">
-        <v>0.62960634198439247</v>
+        <v>0.62892469757546143</v>
       </c>
       <c r="D213" s="22">
         <v>0.56360552443267364</v>
@@ -13592,7 +13525,7 @@
         <v>268</v>
       </c>
       <c r="C216" s="22">
-        <v>0.59355260125654552</v>
+        <v>0.59086275011740108</v>
       </c>
       <c r="D216" s="22">
         <v>0.50039866371748865</v>
@@ -13844,7 +13777,7 @@
         <v>294</v>
       </c>
       <c r="C234" s="22">
-        <v>0.41675936884162867</v>
+        <v>0.38985334037328956</v>
       </c>
       <c r="D234" s="22">
         <v>0.33330607111754285</v>
@@ -13872,7 +13805,7 @@
         <v>296</v>
       </c>
       <c r="C236" s="22">
-        <v>0.41675936884162867</v>
+        <v>0.45482646164121632</v>
       </c>
       <c r="D236" s="22">
         <v>0.36826737508883856</v>
@@ -14124,7 +14057,7 @@
         <v>324</v>
       </c>
       <c r="C254" s="22">
-        <v>0.25798079085832115</v>
+        <v>0.25760621194354938</v>
       </c>
       <c r="D254" s="22">
         <v>0.24767890683233218</v>
@@ -14138,7 +14071,7 @@
         <v>325</v>
       </c>
       <c r="C255" s="22">
-        <v>0.34430386524300105</v>
+        <v>0.33532090457607477</v>
       </c>
       <c r="D255" s="22">
         <v>0.2838412847523748</v>
@@ -14726,7 +14659,7 @@
         <v>375</v>
       </c>
       <c r="C297" s="22">
-        <v>0.36742739086084253</v>
+        <v>0.4275552259460691</v>
       </c>
       <c r="D297" s="22">
         <v>0.32384501252762754</v>
@@ -14740,7 +14673,7 @@
         <v>376</v>
       </c>
       <c r="C298" s="22">
-        <v>0.4275552259460691</v>
+        <v>0.36278560288231398</v>
       </c>
       <c r="D298" s="22">
         <v>0.37954899367730932</v>
@@ -14754,7 +14687,7 @@
         <v>377</v>
       </c>
       <c r="C299" s="22">
-        <v>0.36278560288231398</v>
+        <v>0.36742739086084253</v>
       </c>
       <c r="D299" s="22">
         <v>0.31071946390496508</v>
@@ -15020,7 +14953,7 @@
         <v>402</v>
       </c>
       <c r="C318" s="22">
-        <v>0.35148003017679819</v>
+        <v>0.34476973526209553</v>
       </c>
       <c r="D318" s="22">
         <v>0.31441849730859461</v>
@@ -15048,7 +14981,7 @@
         <v>405</v>
       </c>
       <c r="C320" s="22">
-        <v>0.38729062960357785</v>
+        <v>0.37880350555847242</v>
       </c>
       <c r="D320" s="22">
         <v>0.34476693812893178</v>
@@ -15174,8 +15107,7 @@
         <v>416</v>
       </c>
       <c r="C329" s="22">
-        <f>AVERAGE(C318,C320)</f>
-        <v>0.36938532989018802</v>
+        <v>0.44178384833265194</v>
       </c>
       <c r="D329" s="22">
         <v>0.42700849385463879</v>
@@ -33560,14 +33492,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF366A2-92C5-452E-A51A-E69A98F677EE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>